--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487646_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487646_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.6426</v>
+        <v>9.5824</v>
       </c>
       <c r="E2" t="n">
-        <v>5.48</v>
+        <v>6.2017</v>
       </c>
       <c r="F2" t="n">
-        <v>3.1626</v>
+        <v>3.3807</v>
       </c>
       <c r="G2" t="n">
         <v>5.4296</v>
@@ -610,13 +610,13 @@
         <v>1.3582</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.9706</v>
+        <v>-0.0308</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.775</v>
+        <v>-0.0533</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1956</v>
+        <v>0.0225</v>
       </c>
       <c r="V2" t="n">
         <v>2.8254</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.0138</v>
+        <v>6.8524</v>
       </c>
       <c r="E3" t="n">
-        <v>5.8526</v>
+        <v>5.4733</v>
       </c>
       <c r="F3" t="n">
-        <v>1.1611</v>
+        <v>1.3792</v>
       </c>
       <c r="G3" t="n">
         <v>6.9365</v>
@@ -688,13 +688,13 @@
         <v>1.5523</v>
       </c>
       <c r="S3" t="n">
-        <v>0.437</v>
+        <v>0.2756</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4867</v>
+        <v>0.1074</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0498</v>
+        <v>0.1683</v>
       </c>
       <c r="V3" t="n">
         <v>-0.9418</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.7976</v>
+        <v>5.6067</v>
       </c>
       <c r="E4" t="n">
-        <v>2.8495</v>
+        <v>2.9311</v>
       </c>
       <c r="F4" t="n">
-        <v>2.9482</v>
+        <v>2.6756</v>
       </c>
       <c r="G4" t="n">
         <v>3.1645</v>
@@ -766,13 +766,13 @@
         <v>1.9403</v>
       </c>
       <c r="S4" t="n">
-        <v>0.157</v>
+        <v>-0.0339</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1077</v>
+        <v>-0.0261</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2647</v>
+        <v>-0.0078</v>
       </c>
       <c r="V4" t="n">
         <v>1.506</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. DIAZ MONTERO</t>
+          <t>J. ATIENZA PEREA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>5.3542</v>
+        <v>5.476</v>
       </c>
       <c r="E5" t="n">
-        <v>2.5248</v>
+        <v>3.8059</v>
       </c>
       <c r="F5" t="n">
-        <v>2.8294</v>
+        <v>1.6701</v>
       </c>
       <c r="G5" t="n">
-        <v>4.0784</v>
+        <v>2.4514</v>
       </c>
       <c r="H5" t="n">
-        <v>1.1905</v>
+        <v>0.4861</v>
       </c>
       <c r="I5" t="n">
-        <v>2.8879</v>
+        <v>1.9654</v>
       </c>
       <c r="J5" t="n">
-        <v>2.9959</v>
+        <v>3.3262</v>
       </c>
       <c r="K5" t="n">
-        <v>1.0422</v>
+        <v>0.1318</v>
       </c>
       <c r="L5" t="n">
-        <v>1.9537</v>
+        <v>3.1944</v>
       </c>
       <c r="M5" t="n">
-        <v>1.0825</v>
+        <v>-0.8748</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1483</v>
+        <v>0.3542</v>
       </c>
       <c r="O5" t="n">
-        <v>0.9343</v>
+        <v>-1.229</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5821</v>
+        <v>2.1344</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9702</v>
+        <v>-0.194</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5523</v>
+        <v>2.3284</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9758</v>
+        <v>-0.0516</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4991</v>
+        <v>-0.5502</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4767</v>
+        <v>0.4986</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.2821</v>
+        <v>0.9418</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.2239</v>
       </c>
       <c r="X5" t="n">
         <v>-0.2821</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. ATIENZA PEREA</t>
+          <t>G. DIAZ MONTERO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>4.7936</v>
+        <v>4.7267</v>
       </c>
       <c r="E6" t="n">
-        <v>3.2053</v>
+        <v>2.3061</v>
       </c>
       <c r="F6" t="n">
-        <v>1.5883</v>
+        <v>2.4206</v>
       </c>
       <c r="G6" t="n">
-        <v>2.4514</v>
+        <v>4.0784</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4861</v>
+        <v>1.1905</v>
       </c>
       <c r="I6" t="n">
-        <v>1.9654</v>
+        <v>2.8879</v>
       </c>
       <c r="J6" t="n">
-        <v>3.3262</v>
+        <v>2.9959</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1318</v>
+        <v>1.0422</v>
       </c>
       <c r="L6" t="n">
-        <v>3.1944</v>
+        <v>1.9537</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.8748</v>
+        <v>1.0825</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3542</v>
+        <v>0.1483</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.229</v>
+        <v>0.9343</v>
       </c>
       <c r="P6" t="n">
-        <v>2.1344</v>
+        <v>0.5821</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.194</v>
+        <v>-0.9702</v>
       </c>
       <c r="R6" t="n">
-        <v>2.3284</v>
+        <v>1.5523</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.734</v>
+        <v>0.3483</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.1508</v>
+        <v>0.2804</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4168</v>
+        <v>0.0679</v>
       </c>
       <c r="V6" t="n">
-        <v>0.9418</v>
+        <v>-0.2821</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2239</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>-0.2821</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. SANCHO PEREZ</t>
+          <t>R. LARDIES GUILLEN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8075</v>
+        <v>1.181</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.9892</v>
+        <v>1.3274</v>
       </c>
       <c r="F7" t="n">
-        <v>2.7967</v>
+        <v>-0.1464</v>
       </c>
       <c r="G7" t="n">
-        <v>1.0655</v>
+        <v>1.4555</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.0562</v>
+        <v>1.6757</v>
       </c>
       <c r="I7" t="n">
-        <v>2.1216</v>
+        <v>-0.2202</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.5014999999999999</v>
+        <v>2.0901</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.6889</v>
+        <v>1.3594</v>
       </c>
       <c r="L7" t="n">
-        <v>1.1874</v>
+        <v>0.7307</v>
       </c>
       <c r="M7" t="n">
-        <v>1.567</v>
+        <v>-0.6346000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>0.6327</v>
+        <v>0.3164</v>
       </c>
       <c r="O7" t="n">
-        <v>0.9343</v>
+        <v>-0.951</v>
       </c>
       <c r="P7" t="n">
-        <v>1.9403</v>
+        <v>1.7463</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.194</v>
       </c>
       <c r="R7" t="n">
         <v>1.9403</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.8789</v>
+        <v>-0.5148</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1683</v>
+        <v>-0.5687</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.7106</v>
+        <v>0.0538</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.3194</v>
+        <v>-1.506</v>
       </c>
       <c r="W7" t="n">
-        <v>-1.3194</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.506</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R. LARDIES GUILLEN</t>
+          <t>A. SANCHO PEREZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7261</v>
+        <v>1.18</v>
       </c>
       <c r="E8" t="n">
-        <v>0.927</v>
+        <v>-1.8075</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2009</v>
+        <v>2.9875</v>
       </c>
       <c r="G8" t="n">
-        <v>1.4555</v>
+        <v>1.0655</v>
       </c>
       <c r="H8" t="n">
-        <v>1.6757</v>
+        <v>-1.0562</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2202</v>
+        <v>2.1216</v>
       </c>
       <c r="J8" t="n">
-        <v>2.0901</v>
+        <v>-0.5014999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>1.3594</v>
+        <v>-1.6889</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7307</v>
+        <v>1.1874</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.6346000000000001</v>
+        <v>1.567</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3164</v>
+        <v>0.6327</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.951</v>
+        <v>0.9343</v>
       </c>
       <c r="P8" t="n">
-        <v>1.7463</v>
+        <v>1.9403</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.194</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>1.9403</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9697</v>
+        <v>-0.5064</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.9691</v>
+        <v>0.0134</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0007</v>
+        <v>-0.5198</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.506</v>
+        <v>-1.3194</v>
       </c>
       <c r="W8" t="n">
+        <v>-1.3194</v>
+      </c>
+      <c r="X8" t="n">
         <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>-1.506</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2192</v>
+        <v>-0.09</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3394</v>
+        <v>-0.5396</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5585</v>
+        <v>0.4495</v>
       </c>
       <c r="G9" t="n">
         <v>-0.7389</v>
@@ -1156,13 +1156,13 @@
         <v>0.3881</v>
       </c>
       <c r="S9" t="n">
-        <v>0.57</v>
+        <v>0.2608</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2434</v>
+        <v>0.0432</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3266</v>
+        <v>0.2176</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>H. PEREZ SANCHEZ</t>
+          <t>A. SIMON DEL CORRAL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.3807</v>
+        <v>-0.486</v>
       </c>
       <c r="E10" t="n">
-        <v>0.35</v>
+        <v>-1.2666</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.7307</v>
+        <v>0.7806999999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2213</v>
+        <v>-0.4294</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.5034</v>
+        <v>0.6261</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7246</v>
+        <v>-1.0555</v>
       </c>
       <c r="J10" t="n">
-        <v>1.0845</v>
+        <v>-0.3896</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.8692</v>
+        <v>0.1153</v>
       </c>
       <c r="L10" t="n">
-        <v>1.9537</v>
+        <v>-0.5049</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.8633</v>
+        <v>-0.0398</v>
       </c>
       <c r="N10" t="n">
-        <v>0.3658</v>
+        <v>0.5108</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.229</v>
+        <v>-0.5506</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.3582</v>
+        <v>1.3582</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.1045</v>
+        <v>-0.194</v>
       </c>
       <c r="R10" t="n">
-        <v>1.7463</v>
+        <v>1.5523</v>
       </c>
       <c r="S10" t="n">
-        <v>1.0861</v>
+        <v>-0.7551</v>
       </c>
       <c r="T10" t="n">
-        <v>0.9118000000000001</v>
+        <v>-0.3054</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1743</v>
+        <v>-0.4497</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.3299</v>
+        <v>-0.6597</v>
       </c>
       <c r="W10" t="n">
-        <v>1.4582</v>
+        <v>-0.3776</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.788</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. SIMON DEL CORRAL</t>
+          <t>H. PEREZ SANCHEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.9558</v>
+        <v>-1.2633</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.6275</v>
+        <v>-0.4508</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6716</v>
+        <v>-0.8125</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.4294</v>
+        <v>0.2213</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6261</v>
+        <v>-0.5034</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.0555</v>
+        <v>0.7246</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.3896</v>
+        <v>1.0845</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1153</v>
+        <v>-0.8692</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5049</v>
+        <v>1.9537</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.0398</v>
+        <v>-0.8633</v>
       </c>
       <c r="N11" t="n">
-        <v>0.5108</v>
+        <v>0.3658</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.5506</v>
+        <v>-1.229</v>
       </c>
       <c r="P11" t="n">
-        <v>1.3582</v>
+        <v>-1.3582</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.194</v>
+        <v>-3.1045</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5523</v>
+        <v>1.7463</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.225</v>
+        <v>0.2036</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6662</v>
+        <v>0.111</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5588</v>
+        <v>0.0926</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.6597</v>
+        <v>-0.3299</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.3776</v>
+        <v>1.4582</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.2821</v>
+        <v>-1.788</v>
       </c>
     </row>
     <row r="12">
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.9951</v>
+        <v>-1.8345</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.291</v>
+        <v>-2.1303</v>
       </c>
       <c r="F12" t="n">
         <v>0.2958</v>
@@ -1390,10 +1390,10 @@
         <v>2.1344</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6909</v>
+        <v>-0.5302</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2894</v>
+        <v>-0.1287</v>
       </c>
       <c r="U12" t="n">
         <v>-0.4015</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>30.023</v>
+        <v>30.9314</v>
       </c>
       <c r="E13" t="n">
-        <v>14.9421</v>
+        <v>15.8507</v>
       </c>
       <c r="F13" t="n">
-        <v>15.0806</v>
+        <v>15.0808</v>
       </c>
       <c r="G13" t="n">
         <v>21.36</v>
@@ -1444,7 +1444,7 @@
         <v>19.2338</v>
       </c>
       <c r="K13" t="n">
-        <v>5.552900000000001</v>
+        <v>5.552899999999999</v>
       </c>
       <c r="L13" t="n">
         <v>13.6809</v>
@@ -1468,19 +1468,19 @@
         <v>18.4332</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.2432</v>
+        <v>-1.3345</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.9855</v>
+        <v>-1.077</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2579</v>
+        <v>-0.2575</v>
       </c>
       <c r="V13" t="n">
-        <v>0.2343</v>
+        <v>0.2343000000000005</v>
       </c>
       <c r="W13" t="n">
-        <v>5.4552</v>
+        <v>5.455199999999999</v>
       </c>
       <c r="X13" t="n">
         <v>-5.2208</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.6676</v>
+        <v>1.1455</v>
       </c>
       <c r="E14" t="n">
-        <v>3.7628</v>
+        <v>2.4615</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.0952</v>
+        <v>-1.316</v>
       </c>
       <c r="G14" t="n">
         <v>0.8759</v>
@@ -1546,13 +1546,13 @@
         <v>1.1642</v>
       </c>
       <c r="S14" t="n">
-        <v>2.432</v>
+        <v>0.9099</v>
       </c>
       <c r="T14" t="n">
-        <v>2.0401</v>
+        <v>0.7388</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3919</v>
+        <v>0.1711</v>
       </c>
       <c r="V14" t="n">
         <v>0.3299</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-2.0193</v>
+        <v>-1.1917</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.2889</v>
+        <v>0.2116</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.7303</v>
+        <v>-1.4033</v>
       </c>
       <c r="G15" t="n">
         <v>-2.2138</v>
@@ -1624,13 +1624,13 @@
         <v>1.3582</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.9697</v>
+        <v>-0.1422</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6775</v>
+        <v>-0.177</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2923</v>
+        <v>0.0348</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. ARTILES ROMERO</t>
+          <t>P. SÁNCHEZ GUTIERREZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-2.8726</v>
+        <v>-2.3339</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.5248</v>
+        <v>-0.4582</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.3478</v>
+        <v>-1.8758</v>
       </c>
       <c r="G16" t="n">
-        <v>-4.2464</v>
+        <v>-0.2687</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.4551</v>
+        <v>0.7802</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.7913</v>
+        <v>-1.0489</v>
       </c>
       <c r="J16" t="n">
-        <v>-2.4816</v>
+        <v>2.7204</v>
       </c>
       <c r="K16" t="n">
-        <v>-2.6034</v>
+        <v>1.9897</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1218</v>
+        <v>0.7307</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.7648</v>
+        <v>-2.9891</v>
       </c>
       <c r="N16" t="n">
-        <v>0.1483</v>
+        <v>-1.2095</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.9131</v>
+        <v>-1.7796</v>
       </c>
       <c r="P16" t="n">
+        <v>-2.5224</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>-3.1045</v>
+      </c>
+      <c r="R16" t="n">
         <v>0.5821</v>
       </c>
-      <c r="Q16" t="n">
-        <v>-0.194</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0.7761</v>
-      </c>
       <c r="S16" t="n">
-        <v>0.5096000000000001</v>
+        <v>-0.1548</v>
       </c>
       <c r="T16" t="n">
-        <v>0.6449</v>
+        <v>-0.3561</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1352</v>
+        <v>0.2014</v>
       </c>
       <c r="V16" t="n">
+        <v>0.6119</v>
+      </c>
+      <c r="W16" t="n">
         <v>0.2821</v>
       </c>
-      <c r="W16" t="n">
-        <v>1.506</v>
-      </c>
       <c r="X16" t="n">
-        <v>-1.2239</v>
+        <v>0.3299</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. SÁNCHEZ GUTIERREZ</t>
+          <t>G. ARTILES ROMERO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.9862</v>
+        <v>-2.9849</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.0588</v>
+        <v>-0.8250999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.9275</v>
+        <v>-2.1598</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.2687</v>
+        <v>-4.2464</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7802</v>
+        <v>-2.4551</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.0489</v>
+        <v>-1.7913</v>
       </c>
       <c r="J17" t="n">
-        <v>2.7204</v>
+        <v>-2.4816</v>
       </c>
       <c r="K17" t="n">
-        <v>1.9897</v>
+        <v>-2.6034</v>
       </c>
       <c r="L17" t="n">
-        <v>0.7307</v>
+        <v>0.1218</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.9891</v>
+        <v>-1.7648</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.2095</v>
+        <v>0.1483</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.7796</v>
+        <v>-1.9131</v>
       </c>
       <c r="P17" t="n">
-        <v>-2.5224</v>
+        <v>0.5821</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.1045</v>
+        <v>-0.194</v>
       </c>
       <c r="R17" t="n">
-        <v>0.5821</v>
+        <v>0.7761</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8071</v>
+        <v>0.3973</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.9567</v>
+        <v>0.3446</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1497</v>
+        <v>0.0527</v>
       </c>
       <c r="V17" t="n">
-        <v>0.6119</v>
+        <v>0.2821</v>
       </c>
       <c r="W17" t="n">
-        <v>0.2821</v>
+        <v>1.506</v>
       </c>
       <c r="X17" t="n">
-        <v>0.3299</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.1331</v>
+        <v>-3.3601</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.9891</v>
+        <v>-1.889</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.144</v>
+        <v>-1.4711</v>
       </c>
       <c r="G18" t="n">
         <v>-1.4663</v>
@@ -1858,13 +1858,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1689</v>
+        <v>-0.058</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7268</v>
+        <v>-0.6267</v>
       </c>
       <c r="U18" t="n">
-        <v>0.8957000000000001</v>
+        <v>0.5687</v>
       </c>
       <c r="V18" t="n">
         <v>-1.8358</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. VAZQUEZ JEREZ</t>
+          <t>E. VIDAL RODRIGUEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-4.0457</v>
+        <v>-4.1155</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.4805</v>
+        <v>-2.9796</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.5652</v>
+        <v>-1.1359</v>
       </c>
       <c r="G19" t="n">
-        <v>-6.1897</v>
+        <v>-1.9849</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.7262</v>
+        <v>-0.3955</v>
       </c>
       <c r="I19" t="n">
-        <v>-3.4635</v>
+        <v>-1.5894</v>
       </c>
       <c r="J19" t="n">
-        <v>-4.1519</v>
+        <v>-0.4981</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.1956</v>
+        <v>-0.5437</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.9564</v>
+        <v>0.0456</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.0377</v>
+        <v>-1.4867</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5306</v>
+        <v>0.1483</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.5071</v>
+        <v>-1.635</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.9702</v>
+        <v>-1.9403</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.1344</v>
+        <v>-2.9105</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1642</v>
+        <v>0.9702</v>
       </c>
       <c r="S19" t="n">
-        <v>1.1828</v>
+        <v>0.7514999999999999</v>
       </c>
       <c r="T19" t="n">
-        <v>1.2999</v>
+        <v>0.1469</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1171</v>
+        <v>0.6046</v>
       </c>
       <c r="V19" t="n">
-        <v>1.9314</v>
+        <v>-0.9418</v>
       </c>
       <c r="W19" t="n">
-        <v>1.506</v>
+        <v>0.2821</v>
       </c>
       <c r="X19" t="n">
-        <v>0.4254</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>E. VIDAL RODRIGUEZ</t>
+          <t>D. VAZQUEZ JEREZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.1155</v>
+        <v>-4.5311</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.9796</v>
+        <v>-4.1812</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.1359</v>
+        <v>-0.3499</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.9849</v>
+        <v>-6.1897</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3955</v>
+        <v>-2.7262</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.5894</v>
+        <v>-3.4635</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.4981</v>
+        <v>-4.1519</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.5437</v>
+        <v>-2.1956</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0456</v>
+        <v>-1.9564</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.4867</v>
+        <v>-2.0377</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1483</v>
+        <v>-0.5306</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.635</v>
+        <v>-1.5071</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.9403</v>
+        <v>-0.9702</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.9105</v>
+        <v>-2.1344</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9702</v>
+        <v>1.1642</v>
       </c>
       <c r="S20" t="n">
-        <v>0.7514999999999999</v>
+        <v>0.6973</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1469</v>
+        <v>0.5992</v>
       </c>
       <c r="U20" t="n">
-        <v>0.6046</v>
+        <v>0.0982</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.9418</v>
+        <v>1.9314</v>
       </c>
       <c r="W20" t="n">
-        <v>0.2821</v>
+        <v>1.506</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2239</v>
+        <v>0.4254</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.6208</v>
+        <v>-5.2387</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.733</v>
+        <v>-2.4327</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.8878</v>
+        <v>-2.806</v>
       </c>
       <c r="G21" t="n">
         <v>-2.3914</v>
@@ -2092,13 +2092,13 @@
         <v>0.5821</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2607</v>
+        <v>0.1214</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8838</v>
+        <v>-0.5835</v>
       </c>
       <c r="U21" t="n">
-        <v>0.6232</v>
+        <v>0.7049</v>
       </c>
       <c r="V21" t="n">
         <v>0.3299</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-7.8974</v>
+        <v>-6.7451</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.7889</v>
+        <v>-4.9881</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.1085</v>
+        <v>-1.757</v>
       </c>
       <c r="G22" t="n">
         <v>-3.475</v>
@@ -2170,13 +2170,13 @@
         <v>1.1642</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7642</v>
+        <v>0.3881</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6292</v>
+        <v>0.1716</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.135</v>
+        <v>0.2165</v>
       </c>
       <c r="V22" t="n">
         <v>-0.9418</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-30.023</v>
+        <v>-29.3555</v>
       </c>
       <c r="E23" t="n">
         <v>-15.0808</v>
       </c>
       <c r="F23" t="n">
-        <v>-14.9422</v>
+        <v>-14.2748</v>
       </c>
       <c r="G23" t="n">
         <v>-21.3603</v>
@@ -2224,16 +2224,16 @@
         <v>-2.1261</v>
       </c>
       <c r="K23" t="n">
-        <v>-3.600100000000001</v>
+        <v>-3.6001</v>
       </c>
       <c r="L23" t="n">
-        <v>1.4738</v>
+        <v>1.473800000000001</v>
       </c>
       <c r="M23" t="n">
         <v>-19.2338</v>
       </c>
       <c r="N23" t="n">
-        <v>-5.5531</v>
+        <v>-5.553100000000001</v>
       </c>
       <c r="O23" t="n">
         <v>-13.6808</v>
@@ -2248,16 +2248,16 @@
         <v>7.7613</v>
       </c>
       <c r="S23" t="n">
-        <v>2.2431</v>
+        <v>2.9105</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2577999999999998</v>
+        <v>0.2577999999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>1.9855</v>
+        <v>2.6529</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.2342</v>
+        <v>-0.2342000000000002</v>
       </c>
       <c r="W23" t="n">
         <v>5.221</v>
